--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woofu\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC5EDC0-7F34-47BF-9FFF-BD2D807EBE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AAE7C6-2150-4FBC-AC4C-81F36E19F983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12072" uniqueCount="6085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12072" uniqueCount="6086">
   <si>
     <t>Serial Number</t>
   </si>
@@ -18275,6 +18275,9 @@
   </si>
   <si>
     <t>Chapter 56</t>
+  </si>
+  <si>
+    <t>符號;標誌;簽名</t>
   </si>
 </sst>
 </file>
@@ -18368,7 +18371,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -69818,10 +69821,10 @@
         <v>6065</v>
       </c>
       <c r="D3007" s="3" t="s">
-        <v>6066</v>
+        <v>6085</v>
       </c>
       <c r="E3007" s="3" t="s">
-        <v>133</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3008" spans="1:5" x14ac:dyDescent="0.3">
